--- a/DATA/MASTER/C11_MASTER/Universo_Analitico/ranking_ipml_integracion_dimensiones.xlsx
+++ b/DATA/MASTER/C11_MASTER/Universo_Analitico/ranking_ipml_integracion_dimensiones.xlsx
@@ -486,42 +486,42 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>Puntaje_Redundancia</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Puntaje_Multicolinealidad</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Categoria</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Importancia</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Peso</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Puntaje_Conocimiento_Dominio</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>% Cobertura</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Puntaje_Calidad</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Puntaje_Redundancia</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Puntaje_Multicolinealidad</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Precipitacion_mm</t>
+          <t>ONI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -562,11 +562,11 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1.898</v>
+        <v>2.084</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -575,38 +575,38 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Climática</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Variabilidad Climática</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P2" t="n">
         <v>3</v>
       </c>
-      <c r="O2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" t="n">
         <v>100</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ONI</t>
+          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -647,11 +647,11 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1.265</v>
+        <v>3.619</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -660,38 +660,38 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Variabilidad Climática</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
         <v>3</v>
       </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" t="n">
         <v>100</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -711,7 +711,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Radiacion_Solar</t>
+          <t>Precipitacion_mm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -732,11 +732,11 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1.704</v>
+        <v>1.99</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -745,38 +745,38 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
         <v>3</v>
       </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" t="n">
         <v>100</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Humedad_Relativa</t>
+          <t>Radiacion_Solar</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -817,57 +817,57 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>7.128</v>
+        <v>2.449</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Sin restricciones importantes.</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" t="inlineStr">
         <is>
           <t>Climática</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="O5" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
         <v>100</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
       <c r="S5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nivel_Minimo</t>
+          <t>irca</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -902,11 +902,11 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1.027</v>
+        <v>2.144</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -915,44 +915,44 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Hidrológica</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
         <v>3</v>
       </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>16.48</v>
-      </c>
       <c r="Q6" t="n">
-        <v>0.165</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9165</v>
+        <v>1</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>VolumenUtilDiarioMasa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -987,11 +987,11 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.815</v>
+        <v>2.114</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1000,44 +1000,44 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Hidrológica</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
         <v>3</v>
       </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>9.470000000000001</v>
-      </c>
       <c r="Q7" t="n">
-        <v>0.095</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>63.64</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0.636</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9095</v>
+        <v>0.9636</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
+          <t>Humedad_Relativa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1072,57 +1072,57 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2.97</v>
+        <v>9.391</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
         <v>3</v>
       </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
-      <c r="P8" t="n">
-        <v>9.279999999999999</v>
-      </c>
       <c r="Q8" t="n">
-        <v>0.093</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9093</v>
+        <v>0.95</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Temp_Min_C</t>
+          <t>Nivel_Minimo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1157,57 +1157,57 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>10.573</v>
+        <v>1.028</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Climática</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Hidrológica</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="n">
-        <v>1</v>
-      </c>
-      <c r="P9" t="n">
-        <v>100</v>
-      </c>
       <c r="Q9" t="n">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>16.48</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5</v>
+        <v>0.165</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9</v>
+        <v>0.9165</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AGUAS RESIDUALES TRATADAS</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1242,11 +1242,11 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1.63</v>
+        <v>2.878</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1255,48 +1255,48 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
         <v>3</v>
       </c>
-      <c r="O10" t="n">
-        <v>1</v>
-      </c>
-      <c r="P10" t="n">
-        <v>18.18</v>
-      </c>
       <c r="Q10" t="n">
-        <v>0.182</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.833</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0.095</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8681</v>
+        <v>0.9095</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mes</t>
+          <t>DEMANDA QUIMICA DE OXIGENO (DQO)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1327,11 +1327,11 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1.152</v>
+        <v>2.999</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1340,48 +1340,48 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Temporal</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>2</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.667</v>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P11" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="n">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>1</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0.093</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8668</v>
+        <v>0.9093</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Velocidad_Viento</t>
+          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1412,11 +1412,11 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1.477</v>
+        <v>1.965</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1425,48 +1425,48 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Climática</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.667</v>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P12" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>4.92</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0.049</v>
       </c>
       <c r="T12" t="n">
-        <v>0.8668</v>
+        <v>0.9049</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>irca</t>
+          <t>Temp_Min_C</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1497,11 +1497,11 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>13.982</v>
+        <v>13.221</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1510,48 +1510,48 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
         <v>3</v>
       </c>
-      <c r="O13" t="n">
-        <v>1</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
         <v>100</v>
       </c>
-      <c r="Q13" t="n">
-        <v>1</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.833</v>
-      </c>
       <c r="S13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8499</v>
+        <v>0.9</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1561,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VolumenUtilDiarioMasa</t>
+          <t>Mes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1582,57 +1582,57 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>11.557</v>
+        <v>1.25</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Hidrológica</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
       <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R14" t="n">
         <v>100</v>
       </c>
-      <c r="Q14" t="n">
-        <v>1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.833</v>
-      </c>
       <c r="S14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8499</v>
+        <v>0.8668</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CALIDAD DEL AGUA</t>
+          <t>Velocidad_Viento</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1655,69 +1655,69 @@
         </is>
       </c>
       <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Muy Baja</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>2.574</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
         <v>2</v>
       </c>
-      <c r="E15" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Baja redundancia estructural.</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>4.372</v>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Variable con baja dependencia estructural.</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>3</v>
-      </c>
-      <c r="O15" t="n">
-        <v>1</v>
-      </c>
-      <c r="P15" t="n">
-        <v>18.18</v>
-      </c>
       <c r="Q15" t="n">
-        <v>0.182</v>
+        <v>0.667</v>
       </c>
       <c r="R15" t="n">
-        <v>0.667</v>
+        <v>100</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8183</v>
+        <v>0.8668</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1752,11 +1752,11 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>7.427</v>
+        <v>7.54</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1765,44 +1765,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Sin restricciones importantes.</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N16" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
         <v>3</v>
       </c>
-      <c r="O16" t="n">
-        <v>1</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>1</v>
+      </c>
+      <c r="R16" t="n">
         <v>9.470000000000001</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.095</v>
       </c>
-      <c r="R16" t="n">
-        <v>0.833</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.75</v>
-      </c>
       <c r="T16" t="n">
-        <v>0.8094</v>
+        <v>0.8595</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DEMANDA BIOQUIMICA DE OXIGENO (DBO5)</t>
+          <t>SOLIDOS SUSPENDIDOS TOTALES</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1825,73 +1825,73 @@
         </is>
       </c>
       <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Muy Baja</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>2.722</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Baja</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Baja redundancia estructural.</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>1.934</v>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Variable con baja dependencia estructural.</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>3</v>
-      </c>
-      <c r="O17" t="n">
-        <v>1</v>
-      </c>
-      <c r="P17" t="n">
-        <v>4.92</v>
-      </c>
       <c r="Q17" t="n">
-        <v>0.049</v>
+        <v>0.667</v>
       </c>
       <c r="R17" t="n">
-        <v>0.667</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0.095</v>
       </c>
       <c r="T17" t="n">
-        <v>0.805</v>
+        <v>0.7763</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Media</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Temp_Max_C</t>
+          <t>TEMPERATURA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1922,57 +1922,57 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>31.915</v>
+        <v>2.965</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Climática</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>3</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1</v>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
       </c>
       <c r="P18" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="R18" t="n">
-        <v>0.833</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>0.25</v>
+        <v>0.095</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.7763</v>
       </c>
       <c r="U18" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Temp_Media_C</t>
+          <t>TURBIDEZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2007,57 +2007,57 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>36.048</v>
+        <v>1.645</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Baja</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Climática</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>3</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
       </c>
       <c r="P19" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0.667</v>
       </c>
       <c r="R19" t="n">
-        <v>0.833</v>
+        <v>6.44</v>
       </c>
       <c r="S19" t="n">
-        <v>0.25</v>
+        <v>0.064</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7999000000000001</v>
+        <v>0.7732</v>
       </c>
       <c r="U19" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>TEMPERATURA</t>
+          <t>Anio</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2080,10 +2080,10 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2092,11 +2092,11 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.883</v>
+        <v>4.188</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2105,44 +2105,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.667</v>
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Temporal</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
       </c>
       <c r="P20" t="n">
-        <v>9.470000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.095</v>
+        <v>0.333</v>
       </c>
       <c r="R20" t="n">
-        <v>0.833</v>
+        <v>100</v>
       </c>
       <c r="S20" t="n">
         <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7262</v>
+        <v>0.7332</v>
       </c>
       <c r="U20" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SOLIDOS SUSPENDIDOS TOTALES</t>
+          <t>CALIDAD DEL AGUA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2168,66 +2168,66 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2.705</v>
+        <v>6.742</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N21" t="inlineStr">
         <is>
           <t>Calidad del Agua</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
-        <v>2</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.667</v>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P21" t="n">
-        <v>9.470000000000001</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.095</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>0.833</v>
+        <v>18.18</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0.182</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7262</v>
+        <v>0.7181999999999999</v>
       </c>
       <c r="U21" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TURBIDEZ</t>
+          <t>COBERTURA DE ALCANTARILLADO URBANO</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2253,20 +2253,20 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1.619</v>
+        <v>3.032</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2275,44 +2275,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta baja multicolinealidad respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
+          <t>Sin señal crítica de multicolinealidad bajo este criterio.</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>2</v>
       </c>
-      <c r="O22" t="n">
+      <c r="Q22" t="n">
         <v>0.667</v>
       </c>
-      <c r="P22" t="n">
-        <v>6.44</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.064</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.833</v>
+        <v>100</v>
       </c>
       <c r="S22" t="n">
         <v>1</v>
       </c>
       <c r="T22" t="n">
-        <v>0.7231</v>
+        <v>0.7168</v>
       </c>
       <c r="U22" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Anio</t>
+          <t>ACCESO A AGUA POTABLE ADECUADO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2335,73 +2335,73 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.779</v>
+        <v>37.091</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Moderada</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Existe una dependencia moderada aceptable para modelado.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Sin restricciones importantes.</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Temporal</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1</v>
+      </c>
+      <c r="R23" t="n">
+        <v>100</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="U23" t="inlineStr">
         <is>
           <t>Media</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>1</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="P23" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0.6832</v>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Baja</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CONTINUIDAD DE ACUEDUCTO URBANO</t>
+          <t>Temp_Max_C</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2420,23 +2420,23 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2354914.55</v>
+        <v>36.388</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -2445,48 +2445,48 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>2</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.667</v>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P24" t="n">
-        <v>18.18</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.182</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="S24" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
-        <v>0.635</v>
+        <v>0.7</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FOSFORO TOTAL</t>
+          <t>Temp_Media_C</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2508,70 +2508,70 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>14.153</v>
+        <v>82.34</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N25" t="n">
-        <v>2</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.667</v>
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Climática</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
       </c>
       <c r="P25" t="n">
-        <v>9.279999999999999</v>
+        <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.093</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0.833</v>
+        <v>100</v>
       </c>
       <c r="S25" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
-        <v>0.626</v>
+        <v>0.7</v>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Media</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2581,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NITROGENO TOTAL</t>
+          <t>CONTINUIDAD DE ACUEDUCTO URBANO</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2590,10 +2590,10 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0.167</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2602,57 +2602,55 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>10.296</v>
-      </c>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
+          <t>No Calculado</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>VIF no calculable por varianza nula de la variable.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Evaluar por separado debido a varianza nula; el VIF no es calculable.</t>
+        </is>
+      </c>
+      <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Presenta una dependencia considerable con otras variables.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Analizar conjuntamente con otras variables.</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>2</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.667</v>
       </c>
-      <c r="P26" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0.055</v>
-      </c>
       <c r="R26" t="n">
-        <v>0.833</v>
+        <v>18.18</v>
       </c>
       <c r="S26" t="n">
-        <v>0.5</v>
+        <v>0.182</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6222</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="U26" t="inlineStr">
         <is>
@@ -2666,7 +2664,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CONDUCTIVIDAD ELECTRICA</t>
+          <t>NITROGENO TOTAL</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2675,69 +2673,69 @@
         </is>
       </c>
       <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Muy Baja</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>No presenta relaciones fuertes bajo el criterio definido.</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>10.278</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
+        </is>
+      </c>
+      <c r="L27" t="n">
+        <v>1</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
         <v>2</v>
       </c>
-      <c r="E27" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Baja</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Baja redundancia estructural.</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>22.078</v>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Comparte gran parte de su información con otras variables.</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Revisar antes del entrenamiento de modelos.</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Calidad del Agua</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>2</v>
-      </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.667</v>
       </c>
-      <c r="P27" t="n">
-        <v>9.470000000000001</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.095</v>
-      </c>
       <c r="R27" t="n">
-        <v>0.667</v>
+        <v>5.49</v>
       </c>
       <c r="S27" t="n">
-        <v>0.25</v>
+        <v>0.055</v>
       </c>
       <c r="T27" t="n">
-        <v>0.5264</v>
+        <v>0.6723</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -2751,7 +2749,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>INDICE DE DESEMPENO INSTITUCIONAL</t>
+          <t>COBERTURA DE ALCANTARILLADO RURAL</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2760,69 +2758,69 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>0.833</v>
+        <v>0.5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>4.434</v>
+        <v>7.181</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Baja</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Variable con baja dependencia estructural.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Variable estable para Machine Learning.</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Institucional</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>2</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.667</v>
       </c>
-      <c r="P28" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0.091</v>
-      </c>
       <c r="R28" t="n">
-        <v>0.167</v>
+        <v>100</v>
       </c>
       <c r="S28" t="n">
         <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>0.526</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
@@ -2836,7 +2834,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ACCESO A AGUA POTABLE ADECUADO</t>
+          <t>AGUAS RESIDUALES TRATADAS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2845,7 +2843,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
@@ -2857,59 +2855,57 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en el máximo relativo de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>5.555</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N29" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N29" t="n">
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Muy Alta</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
         <v>3</v>
       </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
-      <c r="P29" t="n">
-        <v>100</v>
-      </c>
       <c r="Q29" t="n">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>18.18</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="T29" t="n">
-        <v>0.5</v>
+        <v>0.5682</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
@@ -2923,7 +2919,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PORCENTAJE DE LA POBLACION CON ACCESO A METODOS DE SANEAMIENTO ADECUADOS</t>
+          <t>COBERTURA DE ACUEDUCTO RURAL</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2932,71 +2928,69 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>32.439</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N30" t="inlineStr">
         <is>
           <t>Infraestructura</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Muy Alta</t>
-        </is>
-      </c>
-      <c r="N30" t="n">
-        <v>3</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1</v>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
       </c>
       <c r="P30" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="R30" t="n">
         <v>100</v>
       </c>
-      <c r="Q30" t="n">
-        <v>1</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0.5</v>
+        <v>0.5668</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
@@ -3010,7 +3004,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DENSIDAD POBLACIONAL</t>
+          <t>COBERTURA DE ACUEDUCTO URBANO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3019,71 +3013,69 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>42.952</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Demográfica</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Infraestructura</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>2</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>0.667</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>100</v>
       </c>
-      <c r="Q31" t="n">
-        <v>1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0.3668</v>
+        <v>0.5668</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -3097,7 +3089,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>COBERTURA DE ACUEDUCTO RURAL</t>
+          <t>DENSIDAD POBLACIONAL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3106,71 +3098,69 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>1329.161</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Demográfica</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>2</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>0.667</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>100</v>
       </c>
-      <c r="Q32" t="n">
-        <v>1</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>0.3668</v>
+        <v>0.5668</v>
       </c>
       <c r="U32" t="inlineStr">
         <is>
@@ -3184,7 +3174,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>COBERTURA DE ACUEDUCTO URBANO</t>
+          <t>POBLACION TOTAL</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3193,71 +3183,69 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>1182.398</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Demográfica</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>2</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.667</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>100</v>
       </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T33" t="n">
-        <v>0.3668</v>
+        <v>0.5668</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -3271,7 +3259,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>COBERTURA DE ALCANTARILLADO RURAL</t>
+          <t>FOSFORO TOTAL</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3280,71 +3268,69 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>14.559</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Alta</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
+          <t>Considerar la dependencia lineal en la evaluación posterior.</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>2</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>0.667</v>
       </c>
-      <c r="P34" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>1</v>
-      </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>0.093</v>
       </c>
       <c r="T34" t="n">
-        <v>0.3668</v>
+        <v>0.5261</v>
       </c>
       <c r="U34" t="inlineStr">
         <is>
@@ -3358,7 +3344,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>COBERTURA DE ALCANTARILLADO URBANO</t>
+          <t>CONDUCTIVIDAD ELECTRICA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3367,71 +3353,69 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Muy Alta</t>
+          <t>Moderada</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Variable altamente redundante respecto al conjunto.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>inf</t>
-        </is>
+          <t>Participa en un nivel intermedio de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>22.148</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Perfecta</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Información completamente redundante respecto al resto de variables.</t>
+          <t>Se detecta multicolinealidad muy alta respecto al conjunto de variables.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Evaluar cuál variable conservar mediante el IPML.</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Infraestructura</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
+          <t>Revisar multicolinealidad muy alta en conjunto con los demás criterios.</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Calidad del Agua</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>2</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.667</v>
       </c>
-      <c r="P35" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>1</v>
-      </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>0.095</v>
       </c>
       <c r="T35" t="n">
-        <v>0.3668</v>
+        <v>0.4763</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -3445,7 +3429,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>POBLACION TOTAL</t>
+          <t>INDICE DE DESEMPENO INSTITUCIONAL</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3454,52 +3438,70 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Muy Baja</t>
+          <t>Muy Alta</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Variable prácticamente independiente.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Demográfica</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
+          <t>Participa en el máximo relativo de relaciones fuertes detectadas.</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>8.381</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Moderada</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Se detecta multicolinealidad moderada respecto al conjunto de variables.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Mantener bajo observación dentro de la evaluación multivariable.</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Institucional</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>2</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.667</v>
       </c>
-      <c r="P36" t="n">
-        <v>100</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>1</v>
-      </c>
       <c r="R36" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+        <v>9.09</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.4259</v>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>Baja</t>
